--- a/output/roomself_excel/8175.xlsx
+++ b/output/roomself_excel/8175.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>518621</v>
+        <v>82725</v>
       </c>
       <c r="D2" t="n">
-        <v>10752</v>
+        <v>2428</v>
       </c>
       <c r="E2" t="n">
-        <v>1077</v>
+        <v>405</v>
       </c>
       <c r="F2" t="n">
-        <v>698</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102669</v>
+        <v>379002</v>
       </c>
       <c r="D3" t="n">
-        <v>2768</v>
+        <v>7004</v>
       </c>
       <c r="E3" t="n">
-        <v>487</v>
+        <v>793</v>
       </c>
       <c r="F3" t="n">
-        <v>404</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115396</v>
+        <v>102669</v>
       </c>
       <c r="D4" t="n">
-        <v>2884</v>
+        <v>2768</v>
       </c>
       <c r="E4" t="n">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="F4" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74186</v>
+        <v>115396</v>
       </c>
       <c r="D5" t="n">
-        <v>3084</v>
+        <v>2884</v>
       </c>
       <c r="E5" t="n">
-        <v>702</v>
+        <v>499</v>
       </c>
       <c r="F5" t="n">
-        <v>199</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>2632</v>
       </c>
       <c r="E6" t="n">
-        <v>702</v>
+        <v>419</v>
       </c>
       <c r="F6" t="n">
-        <v>683</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -586,10 +586,10 @@
         <v>1568</v>
       </c>
       <c r="E7" t="n">
-        <v>372</v>
+        <v>232</v>
       </c>
       <c r="F7" t="n">
-        <v>232</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91092</v>
+        <v>60825</v>
       </c>
       <c r="D8" t="n">
-        <v>2804</v>
+        <v>2120</v>
       </c>
       <c r="E8" t="n">
-        <v>702</v>
+        <v>383</v>
       </c>
       <c r="F8" t="n">
-        <v>221</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25092</v>
+        <v>56894</v>
       </c>
       <c r="D9" t="n">
-        <v>1268</v>
+        <v>2036</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>293</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -656,6 +656,72 @@
       </c>
       <c r="F10" t="n">
         <v>176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>74186</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3084</v>
+      </c>
+      <c r="E11" t="n">
+        <v>186</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30267</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25092</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1268</v>
+      </c>
+      <c r="E13" t="n">
+        <v>153</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8175.xlsx
+++ b/output/roomself_excel/8175.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>2428</v>
       </c>
-      <c r="E2" t="n">
-        <v>405</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>284</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>345</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +569,49 @@
       <c r="D3" t="n">
         <v>7004</v>
       </c>
-      <c r="E3" t="n">
-        <v>793</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>698</v>
+        <v>592</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>731</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>539</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +629,34 @@
       <c r="D4" t="n">
         <v>2768</v>
       </c>
-      <c r="E4" t="n">
-        <v>465</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>269</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>422</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +673,34 @@
       <c r="D5" t="n">
         <v>2884</v>
       </c>
-      <c r="E5" t="n">
-        <v>499</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>457</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +717,34 @@
       <c r="D6" t="n">
         <v>2632</v>
       </c>
-      <c r="E6" t="n">
-        <v>419</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>135</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>385</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +761,26 @@
       <c r="D7" t="n">
         <v>1568</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>232</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>16</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +797,34 @@
       <c r="D8" t="n">
         <v>2120</v>
       </c>
-      <c r="E8" t="n">
-        <v>383</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>202</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>361</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +841,34 @@
       <c r="D9" t="n">
         <v>2036</v>
       </c>
-      <c r="E9" t="n">
-        <v>293</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>228</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>276</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +885,34 @@
       <c r="D10" t="n">
         <v>1660</v>
       </c>
-      <c r="E10" t="n">
-        <v>307</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>176</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>273</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +929,26 @@
       <c r="D11" t="n">
         <v>3084</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>186</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>22</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +965,18 @@
       <c r="D12" t="n">
         <v>1392</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +993,26 @@
       <c r="D13" t="n">
         <v>1268</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>22</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
